--- a/docs/menu-template.xlsx
+++ b/docs/menu-template.xlsx
@@ -4257,12 +4257,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>96170123456</t>
+          <t>96171819311</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>رقم واتساب المقهى مع رمز البلد، أرقام فقط</t>
+          <t>رقم واتساب الذي تصله الطلبات، مع رمز البلد، أرقام فقط</t>
         </is>
       </c>
     </row>
@@ -4325,60 +4325,100 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>انستغرام</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>الهاتف</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>71 819 311</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>اسم الحساب بدون @</t>
+          <t>رقم الاتصال الظاهر في الموقع</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>إعلان</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>رابط الموقع</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/NZzVyibw7Cs3BuqcA</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>شريط إعلان أعلى الصفحة (اتركه فارغاً لإخفائه)</t>
+          <t>رابط Google Maps للمقهى</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>انستغرام</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barista_alasmar</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>رابط الحساب أو اسمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>فيسبوك</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/1BDUXPa3VV/</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>رابط صفحة فيسبوك</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>إعلان</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>شريط إعلان أعلى الصفحة (اتركه فارغاً لإخفائه)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>التوصيل</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>نعم أو لا</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
